--- a/data/trans_dic/P19F$noche-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,58; 78,1</t>
+          <t>69,65; 78,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,17; 86,18</t>
+          <t>79,31; 86,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,63; 81,92</t>
+          <t>76,49; 81,79</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,55; 80,85</t>
+          <t>75,65; 80,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,56; 82,45</t>
+          <t>77,48; 82,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,49; 81,02</t>
+          <t>77,44; 80,96</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,45; 85,34</t>
+          <t>74,53; 85,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,5; 82,76</t>
+          <t>71,68; 83,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>74,64; 83,15</t>
+          <t>75,09; 82,88</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,62; 79,69</t>
+          <t>75,58; 79,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,96; 82,67</t>
+          <t>78,59; 82,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,9; 80,58</t>
+          <t>77,75; 80,65</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la noche</t>
+          <t>Población que, al menos, se cepilla los dientes por la noche (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>272828; 306271</t>
+          <t>273101; 308690</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>422055; 459424</t>
+          <t>422824; 459288</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>709003; 757939</t>
+          <t>707728; 756730</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>856154; 916246</t>
+          <t>857304; 915999</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>778456; 827534</t>
+          <t>777680; 828503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1655919; 1731444</t>
+          <t>1654862; 1730123</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>180780; 207239</t>
+          <t>180983; 206583</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145735; 168670</t>
+          <t>146087; 170186</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>333380; 371390</t>
+          <t>335402; 370190</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1337058; 1409155</t>
+          <t>1336378; 1408075</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1374296; 1438983</t>
+          <t>1367900; 1435044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2733508; 2827503</t>
+          <t>2727984; 2829733</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$noche-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19F$noche-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,65; 78,72</t>
+          <t>68,94; 78,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,31; 86,16</t>
+          <t>79,05; 85,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76,49; 81,79</t>
+          <t>76,46; 81,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,65; 80,83</t>
+          <t>75,78; 80,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,48; 82,55</t>
+          <t>77,22; 82,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77,44; 80,96</t>
+          <t>77,19; 80,91</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,53; 85,07</t>
+          <t>74,6; 85,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>71,68; 83,5</t>
+          <t>71,39; 82,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75,09; 82,88</t>
+          <t>74,99; 83,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,58; 79,63</t>
+          <t>75,6; 79,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,59; 82,45</t>
+          <t>78,74; 82,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77,75; 80,65</t>
+          <t>77,82; 80,53</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>273101; 308690</t>
+          <t>270331; 307210</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>422824; 459288</t>
+          <t>421390; 457437</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>707728; 756730</t>
+          <t>707424; 756973</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>857304; 915999</t>
+          <t>858778; 916939</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>777680; 828503</t>
+          <t>775086; 828489</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1654862; 1730123</t>
+          <t>1649579; 1729010</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>180983; 206583</t>
+          <t>181150; 207608</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>146087; 170186</t>
+          <t>145508; 168869</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>335402; 370190</t>
+          <t>334962; 370730</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1336378; 1408075</t>
+          <t>1336757; 1410512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1367900; 1435044</t>
+          <t>1370593; 1436853</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2727984; 2829733</t>
+          <t>2730687; 2825665</t>
         </is>
       </c>
     </row>
